--- a/data/S002.xlsx
+++ b/data/S002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://odsi2005-my.sharepoint.com/personal/ibrahim_eltaleb_odsi-energy_com/Documents/ODSI_Desktop/Python/Stramlit/Dash_ODSI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{0A039515-FE95-4DE7-8FAC-2FC41D3A2F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D41EC88-C0F7-44E9-A2CB-1EA7E89DDD12}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{0A039515-FE95-4DE7-8FAC-2FC41D3A2F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B02C70B3-4B3A-4994-9712-39DF5FA2FD54}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="23040" windowHeight="13608" activeTab="1" xr2:uid="{181B259E-6879-4259-B043-0BB521B21892}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{181B259E-6879-4259-B043-0BB521B21892}"/>
   </bookViews>
   <sheets>
     <sheet name="Production History" sheetId="5" r:id="rId1"/>
@@ -10821,19 +10821,16 @@
         <v>0.04</v>
       </c>
       <c r="I6">
-        <v>2.0299999999999998</v>
+        <v>6.2636111111111106</v>
       </c>
       <c r="J6">
-        <f>I6*0.25</f>
-        <v>0.50749999999999995</v>
+        <v>1.5659027777777776</v>
       </c>
       <c r="K6">
-        <f>I6*0.5+1</f>
-        <v>2.0149999999999997</v>
+        <v>4.1318055555555562</v>
       </c>
       <c r="L6">
-        <f>K6*0.3</f>
-        <v>0.60449999999999993</v>
+        <v>1.2395416666666665</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -10862,19 +10859,16 @@
         <v>0.2</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>7.0930555555555559</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J38" si="0">I7*0.25</f>
-        <v>1</v>
+        <v>1.773263888888889</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K38" si="1">I7*0.5+1</f>
-        <v>3</v>
+        <v>4.5465277777777784</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7:L38" si="2">K7*0.3</f>
-        <v>0.89999999999999991</v>
+        <v>1.3639583333333329</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -10903,19 +10897,16 @@
         <v>0.3</v>
       </c>
       <c r="I8">
-        <v>4.5999999999999996</v>
+        <v>8.0533333333333346</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>2.0133333333333336</v>
       </c>
       <c r="K8">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
+        <v>5.0266666666666673</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
-        <v>0.98999999999999988</v>
+        <v>1.5079999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -10944,19 +10935,16 @@
         <v>0.38</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>9.0636111111111131</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
-        <v>1.25</v>
+        <v>2.2659027777777783</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>5.5318055555555565</v>
       </c>
       <c r="L9">
-        <f t="shared" si="2"/>
-        <v>1.05</v>
+        <v>1.6595416666666665</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -10985,19 +10973,16 @@
         <v>0.49</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>10.132222222222223</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>2.5330555555555558</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
+        <v>6.0661111111111126</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
-        <v>1.08</v>
+        <v>1.8198333333333334</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -11026,19 +11011,16 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I11">
-        <v>5.45</v>
+        <v>11.313055555555557</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
-        <v>1.3625</v>
+        <v>2.8282638888888894</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
-        <v>3.7250000000000001</v>
+        <v>6.6565277777777787</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
-        <v>1.1174999999999999</v>
+        <v>1.9969583333333334</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -11067,19 +11049,16 @@
         <v>0.62</v>
       </c>
       <c r="I12">
-        <v>5.66</v>
+        <v>12.610555555555555</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
-        <v>1.415</v>
+        <v>3.1526388888888888</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
-        <v>3.83</v>
+        <v>7.3052777777777775</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
-        <v>1.149</v>
+        <v>2.1915833333333334</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -11108,19 +11087,16 @@
         <v>0.63</v>
       </c>
       <c r="I13">
-        <v>9.1</v>
+        <v>13.9275</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>2.2749999999999999</v>
+        <v>3.4818750000000001</v>
       </c>
       <c r="K13">
-        <f t="shared" si="1"/>
-        <v>5.55</v>
+        <v>7.9637500000000001</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
-        <v>1.6649999999999998</v>
+        <v>2.3891249999999999</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -11149,19 +11125,16 @@
         <v>0.68</v>
       </c>
       <c r="I14">
-        <v>9.5</v>
+        <v>15.160833333333331</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
-        <v>2.375</v>
+        <v>3.7902083333333327</v>
       </c>
       <c r="K14">
-        <f t="shared" si="1"/>
-        <v>5.75</v>
+        <v>8.5804166666666664</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
-        <v>1.7249999999999999</v>
+        <v>2.574125</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -11190,19 +11163,16 @@
         <v>0.73</v>
       </c>
       <c r="I15">
-        <v>9.8800000000000008</v>
+        <v>16.313611111111111</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
-        <v>2.4700000000000002</v>
+        <v>4.0784027777777778</v>
       </c>
       <c r="K15">
-        <f t="shared" si="1"/>
-        <v>5.94</v>
+        <v>9.1568055555555556</v>
       </c>
       <c r="L15">
-        <f t="shared" si="2"/>
-        <v>1.782</v>
+        <v>2.7470416666666666</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -11231,19 +11201,16 @@
         <v>0.81</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>17.378333333333334</v>
       </c>
       <c r="J16">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.3445833333333335</v>
       </c>
       <c r="K16">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9.6891666666666669</v>
       </c>
       <c r="L16">
-        <f t="shared" si="2"/>
-        <v>1.7999999999999998</v>
+        <v>2.9067500000000002</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -11272,19 +11239,16 @@
         <v>0.84</v>
       </c>
       <c r="I17">
-        <v>12</v>
+        <v>18.284166666666668</v>
       </c>
       <c r="J17">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4.5710416666666669</v>
       </c>
       <c r="K17">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <v>10.142083333333334</v>
       </c>
       <c r="L17">
-        <f t="shared" si="2"/>
-        <v>2.1</v>
+        <v>3.0426249999999997</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -11313,19 +11277,16 @@
         <v>0.87</v>
       </c>
       <c r="I18">
-        <v>14</v>
+        <v>19.032499999999999</v>
       </c>
       <c r="J18">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>4.7581249999999997</v>
       </c>
       <c r="K18">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10.516250000000001</v>
       </c>
       <c r="L18">
-        <f t="shared" si="2"/>
-        <v>2.4</v>
+        <v>3.1548750000000001</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -11354,19 +11315,16 @@
         <v>0.92</v>
       </c>
       <c r="I19">
-        <v>16</v>
+        <v>19.739166666666666</v>
       </c>
       <c r="J19">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>4.9347916666666665</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10.869583333333333</v>
       </c>
       <c r="L19">
-        <f t="shared" si="2"/>
-        <v>2.6999999999999997</v>
+        <v>3.260875</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -11395,19 +11353,16 @@
         <v>0.98</v>
       </c>
       <c r="I20">
-        <v>16.5</v>
+        <v>20.473611111111108</v>
       </c>
       <c r="J20">
-        <f t="shared" si="0"/>
-        <v>4.125</v>
+        <v>5.118402777777777</v>
       </c>
       <c r="K20">
-        <f t="shared" si="1"/>
-        <v>9.25</v>
+        <v>11.236805555555556</v>
       </c>
       <c r="L20">
-        <f t="shared" si="2"/>
-        <v>2.7749999999999999</v>
+        <v>3.3710416666666667</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -11436,19 +11391,16 @@
         <v>1.02</v>
       </c>
       <c r="I21">
-        <v>18.8</v>
+        <v>21.291388888888886</v>
       </c>
       <c r="J21">
-        <f t="shared" si="0"/>
-        <v>4.7</v>
+        <v>5.3228472222222214</v>
       </c>
       <c r="K21">
-        <f t="shared" si="1"/>
-        <v>10.4</v>
+        <v>11.645694444444445</v>
       </c>
       <c r="L21">
-        <f t="shared" si="2"/>
-        <v>3.12</v>
+        <v>3.4937083333333336</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -11477,19 +11429,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="I22">
-        <v>19</v>
+        <v>22.215833333333336</v>
       </c>
       <c r="J22">
-        <f t="shared" si="0"/>
-        <v>4.75</v>
+        <v>5.553958333333334</v>
       </c>
       <c r="K22">
-        <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>12.107916666666668</v>
       </c>
       <c r="L22">
-        <f t="shared" si="2"/>
-        <v>3.15</v>
+        <v>3.6323749999999997</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -11518,19 +11467,16 @@
         <v>1.18</v>
       </c>
       <c r="I23">
-        <v>19.25</v>
+        <v>23.218055555555555</v>
       </c>
       <c r="J23">
-        <f t="shared" si="0"/>
-        <v>4.8125</v>
+        <v>5.8045138888888888</v>
       </c>
       <c r="K23">
-        <f t="shared" si="1"/>
-        <v>10.625</v>
+        <v>12.609027777777778</v>
       </c>
       <c r="L23">
-        <f t="shared" si="2"/>
-        <v>3.1875</v>
+        <v>3.7827083333333333</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -11559,19 +11505,16 @@
         <v>1.28</v>
       </c>
       <c r="I24">
-        <v>19.329999999999998</v>
+        <v>24.313055555555554</v>
       </c>
       <c r="J24">
-        <f t="shared" si="0"/>
-        <v>4.8324999999999996</v>
+        <v>6.0782638888888885</v>
       </c>
       <c r="K24">
-        <f t="shared" si="1"/>
-        <v>10.664999999999999</v>
+        <v>13.156527777777777</v>
       </c>
       <c r="L24">
-        <f t="shared" si="2"/>
-        <v>3.1994999999999996</v>
+        <v>3.9469583333333329</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -11600,19 +11543,16 @@
         <v>1.34</v>
       </c>
       <c r="I25">
-        <v>20</v>
+        <v>25.442777777777778</v>
       </c>
       <c r="J25">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6.3606944444444444</v>
       </c>
       <c r="K25">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13.721388888888889</v>
       </c>
       <c r="L25">
-        <f t="shared" si="2"/>
-        <v>3.3</v>
+        <v>4.1164166666666659</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -11641,19 +11581,16 @@
         <v>1.4</v>
       </c>
       <c r="I26">
-        <v>20.329999999999998</v>
+        <v>26.600555555555555</v>
       </c>
       <c r="J26">
-        <f t="shared" si="0"/>
-        <v>5.0824999999999996</v>
+        <v>6.6501388888888888</v>
       </c>
       <c r="K26">
-        <f t="shared" si="1"/>
-        <v>11.164999999999999</v>
+        <v>14.300277777777778</v>
       </c>
       <c r="L26">
-        <f t="shared" si="2"/>
-        <v>3.3494999999999995</v>
+        <v>4.2900833333333326</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -11682,19 +11619,16 @@
         <v>1.45</v>
       </c>
       <c r="I27">
-        <v>22</v>
+        <v>27.763888888888886</v>
       </c>
       <c r="J27">
-        <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>6.9409722222222214</v>
       </c>
       <c r="K27">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14.881944444444443</v>
       </c>
       <c r="L27">
-        <f t="shared" si="2"/>
-        <v>3.5999999999999996</v>
+        <v>4.4645833333333336</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -11723,19 +11657,16 @@
         <v>1.47</v>
       </c>
       <c r="I28">
-        <v>22.33</v>
+        <v>28.908611111111114</v>
       </c>
       <c r="J28">
-        <f t="shared" si="0"/>
-        <v>5.5824999999999996</v>
+        <v>7.2271527777777784</v>
       </c>
       <c r="K28">
-        <f t="shared" si="1"/>
-        <v>12.164999999999999</v>
+        <v>15.454305555555557</v>
       </c>
       <c r="L28">
-        <f t="shared" si="2"/>
-        <v>3.6494999999999997</v>
+        <v>4.6362916666666676</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -11764,19 +11695,16 @@
         <v>1.61</v>
       </c>
       <c r="I29">
-        <v>25</v>
+        <v>30.015555555555562</v>
       </c>
       <c r="J29">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
+        <v>7.5038888888888904</v>
       </c>
       <c r="K29">
-        <f t="shared" si="1"/>
-        <v>13.5</v>
+        <v>16.007777777777779</v>
       </c>
       <c r="L29">
-        <f t="shared" si="2"/>
-        <v>4.05</v>
+        <v>4.8023333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -11805,19 +11733,16 @@
         <v>1.65</v>
       </c>
       <c r="I30">
-        <v>25.66</v>
+        <v>31.088888888888892</v>
       </c>
       <c r="J30">
-        <f t="shared" si="0"/>
-        <v>6.415</v>
+        <v>7.772222222222223</v>
       </c>
       <c r="K30">
-        <f t="shared" si="1"/>
-        <v>13.83</v>
+        <v>16.544444444444448</v>
       </c>
       <c r="L30">
-        <f t="shared" si="2"/>
-        <v>4.149</v>
+        <v>4.9633333333333329</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -11846,19 +11771,16 @@
         <v>1.67</v>
       </c>
       <c r="I31">
-        <v>27</v>
+        <v>32.053888888888885</v>
       </c>
       <c r="J31">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>8.0134722222222212</v>
       </c>
       <c r="K31">
-        <f t="shared" si="1"/>
-        <v>14.5</v>
+        <v>17.026944444444442</v>
       </c>
       <c r="L31">
-        <f t="shared" si="2"/>
-        <v>4.3499999999999996</v>
+        <v>5.1080833333333331</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -11884,19 +11806,16 @@
         <v>1.95</v>
       </c>
       <c r="I32">
-        <v>28</v>
+        <v>32.903888888888886</v>
       </c>
       <c r="J32">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8.2259722222222216</v>
       </c>
       <c r="K32">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17.451944444444443</v>
       </c>
       <c r="L32">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>5.2355833333333335</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -11922,19 +11841,16 @@
         <v>2.0328499999999998</v>
       </c>
       <c r="I33">
-        <v>28</v>
+        <v>33.620555555555555</v>
       </c>
       <c r="J33">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8.4051388888888887</v>
       </c>
       <c r="K33">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>17.810277777777777</v>
       </c>
       <c r="L33">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>5.3430833333333325</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -11960,19 +11876,16 @@
         <v>2.1853500000000001</v>
       </c>
       <c r="I34">
-        <v>29</v>
+        <v>33.971333333333334</v>
       </c>
       <c r="J34">
-        <f t="shared" si="0"/>
-        <v>7.25</v>
+        <v>8.4928333333333335</v>
       </c>
       <c r="K34">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
+        <v>17.985666666666667</v>
       </c>
       <c r="L34">
-        <f t="shared" si="2"/>
-        <v>4.6499999999999995</v>
+        <v>5.3956999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -11998,19 +11911,16 @@
         <v>2.1905600000000001</v>
       </c>
       <c r="I35">
-        <v>32</v>
+        <v>34.304166666666667</v>
       </c>
       <c r="J35">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>8.5760416666666668</v>
       </c>
       <c r="K35">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18.152083333333334</v>
       </c>
       <c r="L35">
-        <f t="shared" si="2"/>
-        <v>5.0999999999999996</v>
+        <v>5.4456250000000006</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -12036,19 +11946,16 @@
         <v>2.3809999999999998</v>
       </c>
       <c r="I36">
-        <v>33</v>
+        <v>34.555555555555557</v>
       </c>
       <c r="J36">
-        <f t="shared" si="0"/>
-        <v>8.25</v>
+        <v>8.6388888888888893</v>
       </c>
       <c r="K36">
-        <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>18.277777777777779</v>
       </c>
       <c r="L36">
-        <f t="shared" si="2"/>
-        <v>5.25</v>
+        <v>5.4833333333333334</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -12074,19 +11981,16 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="I37">
-        <v>34.200000000000003</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="J37">
-        <f t="shared" si="0"/>
-        <v>8.5500000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K37">
-        <f t="shared" si="1"/>
-        <v>18.100000000000001</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="L37">
-        <f t="shared" si="2"/>
-        <v>5.4300000000000006</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -12115,15 +12019,12 @@
         <v>35</v>
       </c>
       <c r="J38">
-        <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
       <c r="K38">
-        <f t="shared" si="1"/>
         <v>18.5</v>
       </c>
       <c r="L38">
-        <f t="shared" si="2"/>
         <v>5.55</v>
       </c>
     </row>
